--- a/bom-out/新建 XLSX 工作表.xlsx
+++ b/bom-out/新建 XLSX 工作表.xlsx
@@ -979,12 +979,12 @@
     <col min="1" max="1" width="122.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="94.5" spans="1:1">
+    <row r="1" ht="54" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="409.5" spans="1:1">
+    <row r="2" ht="229.5" spans="1:1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
